--- a/product_selector_out/STM32N6 series.xlsx
+++ b/product_selector_out/STM32N6 series.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO35"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.56640625" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -998,6 +1004,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1332,6 +1339,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -1669,6 +1681,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2006,6 +2023,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2343,6 +2365,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2680,6 +2707,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3017,6 +3049,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3354,6 +3391,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3691,6 +3733,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4028,6 +4075,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4365,6 +4417,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4702,6 +4759,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -5039,6 +5101,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -5376,6 +5443,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -5713,6 +5785,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -6050,6 +6127,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -6387,6 +6469,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -6724,6 +6811,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -7061,6 +7153,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -7398,6 +7495,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -7735,6 +7837,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -8072,6 +8179,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -8409,6 +8521,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -8746,6 +8863,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -9083,12 +9205,17 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -9111,12 +9238,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -9131,9 +9260,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -9193,7 +9321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO35"/>
+  <dimension ref="A1:BP35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9263,6 +9391,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9606,6 +9735,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9703,6 +9837,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -10035,7 +10170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10372,7 +10512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10709,7 +10854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11046,7 +11196,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11383,7 +11538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11720,7 +11880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12057,7 +12222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12394,7 +12564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12731,7 +12906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13068,7 +13248,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13405,7 +13590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13742,7 +13932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14079,7 +14274,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14416,7 +14616,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14753,7 +14958,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15090,7 +15300,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15427,7 +15642,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15764,7 +15984,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16101,7 +16326,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16438,7 +16668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16775,7 +17010,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17112,7 +17352,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17449,7 +17694,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17786,7 +18036,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17794,8 +18049,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
